--- a/backend/local_storage/leaves.xlsx
+++ b/backend/local_storage/leaves.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,34 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yatra</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
